--- a/cadastro_rede_tamanho_fixo.xlsx
+++ b/cadastro_rede_tamanho_fixo.xlsx
@@ -232,9 +232,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>2238375</xdr:colOff>
+      <xdr:colOff>2344897</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>636126</xdr:rowOff>
+      <xdr:rowOff>850229</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -252,7 +252,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="142875" y="95250"/>
-          <a:ext cx="2095500" cy="540876"/>
+          <a:ext cx="2202022" cy="754979"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -275,9 +275,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>2238375</xdr:colOff>
+      <xdr:colOff>2344897</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>636126</xdr:rowOff>
+      <xdr:rowOff>850229</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -295,7 +295,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="142875" y="95250"/>
-          <a:ext cx="2095500" cy="540876"/>
+          <a:ext cx="2202022" cy="754979"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/cadastro_rede_tamanho_fixo.xlsx
+++ b/cadastro_rede_tamanho_fixo.xlsx
@@ -7,15 +7,21 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Departamento de tecnologia da i" sheetId="1" r:id="rId1"/>
-    <sheet name="obras" sheetId="2" r:id="rId2"/>
+    <sheet name="infra" sheetId="1" r:id="rId1"/>
+    <sheet name="dti" sheetId="2" r:id="rId2"/>
+    <sheet name="Departamento de tecnologia da i" sheetId="3" r:id="rId3"/>
+    <sheet name="obras" sheetId="4" r:id="rId4"/>
+    <sheet name="presidencia" sheetId="5" r:id="rId5"/>
+    <sheet name="cafeteria" sheetId="6" r:id="rId6"/>
+    <sheet name="teste" sheetId="7" r:id="rId7"/>
+    <sheet name="ti" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="113">
   <si>
     <t>CADASTRO DE REDE</t>
   </si>
@@ -26,54 +32,105 @@
     <t>Nome:</t>
   </si>
   <si>
+    <t>teste</t>
+  </si>
+  <si>
+    <t>Matrícula:</t>
+  </si>
+  <si>
+    <t>Login de Rede:</t>
+  </si>
+  <si>
+    <t>a.a</t>
+  </si>
+  <si>
+    <t>E-mail institucional:</t>
+  </si>
+  <si>
+    <t>a@gmail.com</t>
+  </si>
+  <si>
+    <t>Departamento:</t>
+  </si>
+  <si>
+    <t>infra</t>
+  </si>
+  <si>
+    <t>Quantidade de servidores:</t>
+  </si>
+  <si>
+    <t>DADOS DOS SERVIDORES</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>Matrícula</t>
+  </si>
+  <si>
+    <t>Login de Rede</t>
+  </si>
+  <si>
+    <t>E-mail Institucional</t>
+  </si>
+  <si>
+    <t>Coordenação</t>
+  </si>
+  <si>
+    <t>a da silva</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>as.12</t>
+  </si>
+  <si>
+    <t>b@gmail.com</t>
+  </si>
+  <si>
+    <t>dti</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>123444</t>
+  </si>
+  <si>
+    <t>dasda.asd</t>
+  </si>
+  <si>
+    <t>cd@gmail.com</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>444444</t>
+  </si>
+  <si>
+    <t>sis.sdd</t>
+  </si>
+  <si>
+    <t>qw@gmail.com</t>
+  </si>
+  <si>
+    <t>sistema</t>
+  </si>
+  <si>
     <t>adriana</t>
   </si>
   <si>
-    <t>Matrícula:</t>
-  </si>
-  <si>
-    <t>Login de Rede:</t>
-  </si>
-  <si>
     <t>adriana.a</t>
   </si>
   <si>
-    <t>E-mail institucional:</t>
-  </si>
-  <si>
     <t>a@asdas.com</t>
   </si>
   <si>
-    <t>Departamento:</t>
-  </si>
-  <si>
     <t>Departamento de tecnologia da informação</t>
   </si>
   <si>
-    <t>Quantidade de servidores:</t>
-  </si>
-  <si>
-    <t>DADOS DOS SERVIDORES</t>
-  </si>
-  <si>
-    <t>Nome</t>
-  </si>
-  <si>
-    <t>Matrícula</t>
-  </si>
-  <si>
-    <t>Login de Rede</t>
-  </si>
-  <si>
-    <t>E-mail Institucional</t>
-  </si>
-  <si>
-    <t>Coordenação</t>
-  </si>
-  <si>
-    <t>teste</t>
-  </si>
-  <si>
     <t>asd.asd</t>
   </si>
   <si>
@@ -86,6 +143,9 @@
     <t>dasdasd</t>
   </si>
   <si>
+    <t>123123</t>
+  </si>
+  <si>
     <t>qwe.qwe</t>
   </si>
   <si>
@@ -110,7 +170,196 @@
     <t>qweqweqwe</t>
   </si>
   <si>
+    <t>1231231234</t>
+  </si>
+  <si>
     <t>administrativo</t>
+  </si>
+  <si>
+    <t>Roberto</t>
+  </si>
+  <si>
+    <t>eqweqw</t>
+  </si>
+  <si>
+    <t>123wqeqew</t>
+  </si>
+  <si>
+    <t>presidencia</t>
+  </si>
+  <si>
+    <t>qweqwe</t>
+  </si>
+  <si>
+    <t>qweqw</t>
+  </si>
+  <si>
+    <t>adm</t>
+  </si>
+  <si>
+    <t>suporte</t>
+  </si>
+  <si>
+    <t>jorge</t>
+  </si>
+  <si>
+    <t>cafeteria</t>
+  </si>
+  <si>
+    <t>asdasd</t>
+  </si>
+  <si>
+    <t>asdasdas</t>
+  </si>
+  <si>
+    <t>asdasdasd</t>
+  </si>
+  <si>
+    <t>ghjkghjk</t>
+  </si>
+  <si>
+    <t>ghjkghjkf</t>
+  </si>
+  <si>
+    <t>fghjfghj</t>
+  </si>
+  <si>
+    <t>sla</t>
+  </si>
+  <si>
+    <t>lucas</t>
+  </si>
+  <si>
+    <t>khjkhjk</t>
+  </si>
+  <si>
+    <t>ghjghjghj</t>
+  </si>
+  <si>
+    <t>jkhjk</t>
+  </si>
+  <si>
+    <t>gjk</t>
+  </si>
+  <si>
+    <t>hjkghjk</t>
+  </si>
+  <si>
+    <t>ghjfjhk</t>
+  </si>
+  <si>
+    <t>hljklhjkl</t>
+  </si>
+  <si>
+    <t>hklhjk</t>
+  </si>
+  <si>
+    <t>hklhkl</t>
+  </si>
+  <si>
+    <t>hklhjkl</t>
+  </si>
+  <si>
+    <t>hjklhjkl</t>
+  </si>
+  <si>
+    <t>hjklhkghj</t>
+  </si>
+  <si>
+    <t>gjhkjfjkhj</t>
+  </si>
+  <si>
+    <t>mfjhfghmjg</t>
+  </si>
+  <si>
+    <t>mfgyhjmf</t>
+  </si>
+  <si>
+    <t>fmyjfym</t>
+  </si>
+  <si>
+    <t>gustavo</t>
+  </si>
+  <si>
+    <t>test.test</t>
+  </si>
+  <si>
+    <t>asd@gmail</t>
+  </si>
+  <si>
+    <t>ti</t>
+  </si>
+  <si>
+    <t>nfghnf</t>
+  </si>
+  <si>
+    <t>fgnhfg</t>
+  </si>
+  <si>
+    <t>fnghf</t>
+  </si>
+  <si>
+    <t>fgnhfghn</t>
+  </si>
+  <si>
+    <t>mghjghm</t>
+  </si>
+  <si>
+    <t>hgjmghgkf</t>
+  </si>
+  <si>
+    <t>ghfghfgh</t>
+  </si>
+  <si>
+    <t>fghfghffghfg</t>
+  </si>
+  <si>
+    <t>sergio</t>
+  </si>
+  <si>
+    <t>sergio@gmail.com</t>
+  </si>
+  <si>
+    <t>antonio</t>
+  </si>
+  <si>
+    <t>54656456</t>
+  </si>
+  <si>
+    <t>12.123</t>
+  </si>
+  <si>
+    <t>asd@gmail.com</t>
+  </si>
+  <si>
+    <t>carlos</t>
+  </si>
+  <si>
+    <t>8789789</t>
+  </si>
+  <si>
+    <t>asd.awqe</t>
+  </si>
+  <si>
+    <t>silv@gmail.com</t>
+  </si>
+  <si>
+    <t>ernani</t>
+  </si>
+  <si>
+    <t>564.lk</t>
+  </si>
+  <si>
+    <t>22@gmail.com</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>asdasd.13123</t>
+  </si>
+  <si>
+    <t>asdfff@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -265,6 +514,264 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2344897</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>850229</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="niteroi.png"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="142875" y="95250"/>
+          <a:ext cx="2202022" cy="754979"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2344897</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>850229</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="niteroi.png"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="142875" y="95250"/>
+          <a:ext cx="2202022" cy="754979"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2344897</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>850229</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="niteroi.png"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="142875" y="95250"/>
+          <a:ext cx="2202022" cy="754979"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2344897</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>850229</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="niteroi.png"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="142875" y="95250"/>
+          <a:ext cx="2202022" cy="754979"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2344897</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>850229</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="niteroi.png"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="142875" y="95250"/>
+          <a:ext cx="2202022" cy="754979"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2344897</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>850229</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="niteroi.png"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="142875" y="95250"/>
+          <a:ext cx="2202022" cy="754979"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -592,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -635,7 +1142,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="4">
-        <v>111111111</v>
+        <v>123123</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -679,7 +1186,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -715,34 +1222,17 @@
       <c r="A14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="4">
-        <v>1111</v>
+      <c r="B14" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="4">
-        <v>123123</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -758,6 +1248,338 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="45.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="70" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4">
+        <v>123123</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A12:E12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="45.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="70" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4">
+        <v>111111111</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A12:E12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -790,7 +1612,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -812,7 +1634,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -823,7 +1645,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -834,7 +1656,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -879,19 +1701,836 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="4">
-        <v>1231231234</v>
+        <v>48</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A12:E12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="45.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="70" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4">
+        <v>123</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4">
+        <v>5</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A12:E12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="45.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="70" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4">
+        <v>123123</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="D14" s="4" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>31</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A12:E12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="45.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="70" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4">
+        <v>123123</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4">
+        <v>3</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A12:E12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="45.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="70" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4">
+        <v>123</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4">
+        <v>7</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="4">
+        <v>1231234</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="4">
+        <v>23123</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
